--- a/artfynd/A 33391-2022 artfynd.xlsx
+++ b/artfynd/A 33391-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123428678</v>
+        <v>123428381</v>
       </c>
       <c r="B2" t="n">
-        <v>97324</v>
+        <v>5193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384956</v>
+        <v>384954</v>
       </c>
       <c r="R2" t="n">
-        <v>6584495</v>
+        <v>6584505</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123429156</v>
+        <v>123428678</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
+        <v>97324</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384958</v>
+        <v>384956</v>
       </c>
       <c r="R3" t="n">
-        <v>6584502</v>
+        <v>6584495</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123428381</v>
+        <v>123429156</v>
       </c>
       <c r="B5" t="n">
-        <v>5193</v>
+        <v>5173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384954</v>
+        <v>384958</v>
       </c>
       <c r="R5" t="n">
-        <v>6584505</v>
+        <v>6584502</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 33391-2022 artfynd.xlsx
+++ b/artfynd/A 33391-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123428381</v>
+        <v>123429321</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>8430</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384954</v>
+        <v>384972</v>
       </c>
       <c r="R2" t="n">
-        <v>6584505</v>
+        <v>6584531</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -788,7 +788,7 @@
         <v>123428678</v>
       </c>
       <c r="B3" t="n">
-        <v>97324</v>
+        <v>97330</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123429321</v>
+        <v>123428381</v>
       </c>
       <c r="B4" t="n">
-        <v>8430</v>
+        <v>5193</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384972</v>
+        <v>384954</v>
       </c>
       <c r="R4" t="n">
-        <v>6584531</v>
+        <v>6584505</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 33391-2022 artfynd.xlsx
+++ b/artfynd/A 33391-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123429156</v>
+        <v>123429321</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
+        <v>8434</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384958</v>
+        <v>384972</v>
       </c>
       <c r="R2" t="n">
-        <v>6584502</v>
+        <v>6584531</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123428678</v>
+        <v>123429156</v>
       </c>
       <c r="B3" t="n">
-        <v>97333</v>
+        <v>5174</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384956</v>
+        <v>384958</v>
       </c>
       <c r="R3" t="n">
-        <v>6584495</v>
+        <v>6584502</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123429321</v>
+        <v>123428678</v>
       </c>
       <c r="B4" t="n">
-        <v>8430</v>
+        <v>97350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384972</v>
+        <v>384956</v>
       </c>
       <c r="R4" t="n">
-        <v>6584531</v>
+        <v>6584495</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
         <v>123428381</v>
       </c>
       <c r="B5" t="n">
-        <v>5193</v>
+        <v>5194</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 33391-2022 artfynd.xlsx
+++ b/artfynd/A 33391-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123429321</v>
+        <v>123428381</v>
       </c>
       <c r="B2" t="n">
-        <v>8434</v>
+        <v>5196</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384972</v>
+        <v>384954</v>
       </c>
       <c r="R2" t="n">
-        <v>6584531</v>
+        <v>6584505</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -788,7 +788,7 @@
         <v>123429156</v>
       </c>
       <c r="B3" t="n">
-        <v>5174</v>
+        <v>5176</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>123428678</v>
       </c>
       <c r="B4" t="n">
-        <v>97350</v>
+        <v>97367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123428381</v>
+        <v>123429321</v>
       </c>
       <c r="B5" t="n">
-        <v>5194</v>
+        <v>8436</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384954</v>
+        <v>384972</v>
       </c>
       <c r="R5" t="n">
-        <v>6584505</v>
+        <v>6584531</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 33391-2022 artfynd.xlsx
+++ b/artfynd/A 33391-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123428381</v>
+        <v>123429321</v>
       </c>
       <c r="B2" t="n">
-        <v>5196</v>
+        <v>8436</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384954</v>
+        <v>384972</v>
       </c>
       <c r="R2" t="n">
-        <v>6584505</v>
+        <v>6584531</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123429156</v>
+        <v>123428381</v>
       </c>
       <c r="B3" t="n">
-        <v>5176</v>
+        <v>5196</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384958</v>
+        <v>384954</v>
       </c>
       <c r="R3" t="n">
-        <v>6584502</v>
+        <v>6584505</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123428678</v>
+        <v>123429156</v>
       </c>
       <c r="B4" t="n">
-        <v>97367</v>
+        <v>5176</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384956</v>
+        <v>384958</v>
       </c>
       <c r="R4" t="n">
-        <v>6584495</v>
+        <v>6584502</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123429321</v>
+        <v>123428678</v>
       </c>
       <c r="B5" t="n">
-        <v>8436</v>
+        <v>97369</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384972</v>
+        <v>384956</v>
       </c>
       <c r="R5" t="n">
-        <v>6584531</v>
+        <v>6584495</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 33391-2022 artfynd.xlsx
+++ b/artfynd/A 33391-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123429321</v>
+        <v>123428381</v>
       </c>
       <c r="B2" t="n">
-        <v>8436</v>
+        <v>5196</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384972</v>
+        <v>384954</v>
       </c>
       <c r="R2" t="n">
-        <v>6584531</v>
+        <v>6584505</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123428381</v>
+        <v>123429156</v>
       </c>
       <c r="B3" t="n">
-        <v>5196</v>
+        <v>5176</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384954</v>
+        <v>384958</v>
       </c>
       <c r="R3" t="n">
-        <v>6584505</v>
+        <v>6584502</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123429156</v>
+        <v>123429321</v>
       </c>
       <c r="B4" t="n">
-        <v>5176</v>
+        <v>8436</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384958</v>
+        <v>384972</v>
       </c>
       <c r="R4" t="n">
-        <v>6584502</v>
+        <v>6584531</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
         <v>123428678</v>
       </c>
       <c r="B5" t="n">
-        <v>97369</v>
+        <v>96957</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 33391-2022 artfynd.xlsx
+++ b/artfynd/A 33391-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123428381</v>
+        <v>123429321</v>
       </c>
       <c r="B2" t="n">
-        <v>5196</v>
+        <v>8436</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384954</v>
+        <v>384972</v>
       </c>
       <c r="R2" t="n">
-        <v>6584505</v>
+        <v>6584531</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123429156</v>
+        <v>123428381</v>
       </c>
       <c r="B3" t="n">
-        <v>5176</v>
+        <v>5196</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384958</v>
+        <v>384954</v>
       </c>
       <c r="R3" t="n">
-        <v>6584502</v>
+        <v>6584505</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123429321</v>
+        <v>123428678</v>
       </c>
       <c r="B4" t="n">
-        <v>8436</v>
+        <v>96957</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384972</v>
+        <v>384956</v>
       </c>
       <c r="R4" t="n">
-        <v>6584531</v>
+        <v>6584495</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123428678</v>
+        <v>123429156</v>
       </c>
       <c r="B5" t="n">
-        <v>96957</v>
+        <v>5176</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384956</v>
+        <v>384958</v>
       </c>
       <c r="R5" t="n">
-        <v>6584495</v>
+        <v>6584502</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 33391-2022 artfynd.xlsx
+++ b/artfynd/A 33391-2022 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123428381</v>
+        <v>123428678</v>
       </c>
       <c r="B3" t="n">
-        <v>5196</v>
+        <v>96957</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384954</v>
+        <v>384956</v>
       </c>
       <c r="R3" t="n">
-        <v>6584505</v>
+        <v>6584495</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123428678</v>
+        <v>123428381</v>
       </c>
       <c r="B4" t="n">
-        <v>96957</v>
+        <v>5196</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384956</v>
+        <v>384954</v>
       </c>
       <c r="R4" t="n">
-        <v>6584495</v>
+        <v>6584505</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 33391-2022 artfynd.xlsx
+++ b/artfynd/A 33391-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123429321</v>
+        <v>123429156</v>
       </c>
       <c r="B2" t="n">
-        <v>8436</v>
+        <v>5176</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384972</v>
+        <v>384958</v>
       </c>
       <c r="R2" t="n">
-        <v>6584531</v>
+        <v>6584502</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123428381</v>
+        <v>123429321</v>
       </c>
       <c r="B4" t="n">
-        <v>5196</v>
+        <v>8436</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384954</v>
+        <v>384972</v>
       </c>
       <c r="R4" t="n">
-        <v>6584505</v>
+        <v>6584531</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123429156</v>
+        <v>123428381</v>
       </c>
       <c r="B5" t="n">
-        <v>5176</v>
+        <v>5196</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384958</v>
+        <v>384954</v>
       </c>
       <c r="R5" t="n">
-        <v>6584502</v>
+        <v>6584505</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 33391-2022 artfynd.xlsx
+++ b/artfynd/A 33391-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123428381</v>
+        <v>123429156</v>
       </c>
       <c r="B2" t="n">
-        <v>5196</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384954</v>
+        <v>384958</v>
       </c>
       <c r="R2" t="n">
-        <v>6584505</v>
+        <v>6584502</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123429156</v>
+        <v>123428381</v>
       </c>
       <c r="B3" t="n">
-        <v>5176</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384958</v>
+        <v>384954</v>
       </c>
       <c r="R3" t="n">
-        <v>6584502</v>
+        <v>6584505</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +874,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum, Mikael Andersson</t>
+          <t>Mikael Andersson, Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -895,15 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123428678</v>
+        <v>123429321</v>
       </c>
       <c r="B4" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384956</v>
+        <v>384972</v>
       </c>
       <c r="R4" t="n">
-        <v>6584495</v>
+        <v>6584531</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,15 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123429321</v>
+        <v>123428431</v>
       </c>
       <c r="B5" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>208249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1049,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384972</v>
+        <v>384990</v>
       </c>
       <c r="R5" t="n">
-        <v>6584531</v>
+        <v>6584567</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,6 +1088,111 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>NVI Grums-Lång</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123428678</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Grums-Lång, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>384956</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6584495</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Grums</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Borgvik</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mikael Andersson, Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>NVI Grums-Lång</t>
         </is>

--- a/artfynd/A 33391-2022 artfynd.xlsx
+++ b/artfynd/A 33391-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
           <t>NVI Grums-Lång</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123429156</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
           <t>NVI Grums-Lång</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123428381</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
           <t>NVI Grums-Lång</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123429321</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
           <t>NVI Grums-Lång</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123428431</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,8 +1222,20 @@
           <t>NVI Grums-Lång</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123428678</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>